--- a/ig/test-tabs-svs/ValueSet-jdv-j401-categorie-droit-prestation-ms.xlsx
+++ b/ig/test-tabs-svs/ValueSet-jdv-j401-categorie-droit-prestation-ms.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="73">
   <si>
     <t>Property</t>
   </si>
@@ -135,9 +135,6 @@
   </si>
   <si>
     <t>warning-draft</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-j401-categorie-droit-prestation-ms|20260505120000</t>
   </si>
   <si>
     <t>Level</t>
@@ -552,7 +549,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -585,14 +582,6 @@
       </c>
       <c r="B4" t="s" s="2">
         <v>37</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -607,25 +596,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>40</v>
+      </c>
+      <c r="B1" t="s" s="1">
         <v>41</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>42</v>
       </c>
       <c r="C1" t="s" s="1">
         <v>38</v>
       </c>
       <c r="D1" t="s" s="1">
+        <v>42</v>
+      </c>
+      <c r="E1" t="s" s="1">
         <v>43</v>
       </c>
-      <c r="E1" t="s" s="1">
+      <c r="F1" t="s" s="1">
         <v>44</v>
       </c>
-      <c r="F1" t="s" s="1">
+      <c r="G1" t="s" s="1">
         <v>45</v>
-      </c>
-      <c r="G1" t="s" s="1">
-        <v>46</v>
       </c>
     </row>
     <row r="2">
@@ -640,7 +629,7 @@
         <v>31</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F2" t="s" s="2">
         <v>15</v>
@@ -658,10 +647,10 @@
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="E3" t="s" s="2">
         <v>48</v>
-      </c>
-      <c r="E3" t="s" s="2">
-        <v>49</v>
       </c>
       <c r="F3" t="s" s="2">
         <v>15</v>
@@ -679,10 +668,10 @@
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="E4" t="s" s="2">
         <v>50</v>
-      </c>
-      <c r="E4" t="s" s="2">
-        <v>51</v>
       </c>
       <c r="F4" t="s" s="2">
         <v>15</v>
@@ -700,10 +689,10 @@
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="E5" t="s" s="2">
         <v>52</v>
-      </c>
-      <c r="E5" t="s" s="2">
-        <v>53</v>
       </c>
       <c r="F5" t="s" s="2">
         <v>15</v>
@@ -721,10 +710,10 @@
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="E6" t="s" s="2">
         <v>54</v>
-      </c>
-      <c r="E6" t="s" s="2">
-        <v>55</v>
       </c>
       <c r="F6" t="s" s="2">
         <v>15</v>
@@ -742,10 +731,10 @@
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="E7" t="s" s="2">
         <v>56</v>
-      </c>
-      <c r="E7" t="s" s="2">
-        <v>57</v>
       </c>
       <c r="F7" t="s" s="2">
         <v>15</v>
@@ -763,10 +752,10 @@
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="E8" t="s" s="2">
         <v>58</v>
-      </c>
-      <c r="E8" t="s" s="2">
-        <v>59</v>
       </c>
       <c r="F8" t="s" s="2">
         <v>15</v>
@@ -784,10 +773,10 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="E9" t="s" s="2">
         <v>60</v>
-      </c>
-      <c r="E9" t="s" s="2">
-        <v>61</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>15</v>
@@ -805,10 +794,10 @@
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="E10" t="s" s="2">
         <v>62</v>
-      </c>
-      <c r="E10" t="s" s="2">
-        <v>63</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>15</v>
@@ -826,10 +815,10 @@
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E11" t="s" s="2">
         <v>64</v>
-      </c>
-      <c r="E11" t="s" s="2">
-        <v>65</v>
       </c>
       <c r="F11" t="s" s="2">
         <v>15</v>
@@ -847,10 +836,10 @@
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="E12" t="s" s="2">
         <v>66</v>
-      </c>
-      <c r="E12" t="s" s="2">
-        <v>67</v>
       </c>
       <c r="F12" t="s" s="2">
         <v>15</v>
@@ -868,10 +857,10 @@
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="E13" t="s" s="2">
         <v>68</v>
-      </c>
-      <c r="E13" t="s" s="2">
-        <v>69</v>
       </c>
       <c r="F13" t="s" s="2">
         <v>15</v>
@@ -889,10 +878,10 @@
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="E14" t="s" s="2">
         <v>70</v>
-      </c>
-      <c r="E14" t="s" s="2">
-        <v>71</v>
       </c>
       <c r="F14" t="s" s="2">
         <v>15</v>
@@ -910,10 +899,10 @@
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="E15" t="s" s="2">
         <v>72</v>
-      </c>
-      <c r="E15" t="s" s="2">
-        <v>73</v>
       </c>
       <c r="F15" t="s" s="2">
         <v>15</v>
